--- a/SuppXLS/Scen_UC_DECRHEAT_MANHEAT_10_15.xlsx
+++ b/SuppXLS/Scen_UC_DECRHEAT_MANHEAT_10_15.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449EF702-9314-4A38-9F0B-621A338E8CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108C5D4F-6F80-45A1-A522-BFAA9D8C3CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
   <sheets>
-    <sheet name="DECELC_DECEHEAT_20_50" sheetId="1" r:id="rId1"/>
+    <sheet name="DECEHEAT_MANHEAT_20_25" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -92,25 +92,25 @@
     <t>LO</t>
   </si>
   <si>
-    <t>DECELC</t>
-  </si>
-  <si>
     <t>AllRegions</t>
   </si>
   <si>
-    <t>Minimum Decenteralized  ELC penetration</t>
-  </si>
-  <si>
-    <t>UC_DECELC_DECEHEAT_20_50</t>
-  </si>
-  <si>
-    <t>DECEHEAT</t>
-  </si>
-  <si>
-    <t>HEAT</t>
-  </si>
-  <si>
     <t>UC_COMPRD</t>
+  </si>
+  <si>
+    <t>DMD</t>
+  </si>
+  <si>
+    <t>DECRHEAT</t>
+  </si>
+  <si>
+    <t>MANHEAT</t>
+  </si>
+  <si>
+    <t>UC_DECRHEAT_MANHEAT_20_50</t>
+  </si>
+  <si>
+    <t>Minimum Decenteralized  Renewable heat penetration</t>
   </si>
 </sst>
 </file>
@@ -317,7 +317,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> that specifcy the minimum DECELC penetration. The set of renewable technologies is selected using PSet_Set DECEL built in VEDA-BE and now available for VEDA-FE templates.</a:t>
+            <a:t> that specifcy the minimum DECRHEAT penetration. The set of renewable technologies is selected using PSet_Set DECEL built in VEDA-BE and now available for VEDA-FE templates.</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -617,7 +617,7 @@
   <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.33203125" customWidth="1"/>
     <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
@@ -679,7 +679,7 @@
         <v>13</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>14</v>
@@ -693,19 +693,19 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
         <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
       </c>
       <c r="G6" t="s">
         <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I6">
         <v>2030</v>
@@ -717,7 +717,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -726,24 +726,24 @@
         <v>15</v>
       </c>
       <c r="O6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
         <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
       </c>
       <c r="G7" t="s">
         <v>22</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I7">
         <v>2050</v>
@@ -755,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -764,7 +764,7 @@
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
